--- a/xlsx/換色紀錄表(8).xlsx
+++ b/xlsx/換色紀錄表(8).xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{5FB2DB27-1F5C-5F4C-B998-09180E8E0EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F681B00-7548-456F-A970-4D1D7CC0C4CC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{44F9F003-FDB2-3347-882A-53263BF13D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="75" windowWidth="18960" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2128,11 +2128,11 @@
       </c>
       <c r="E2" s="27">
         <f ca="1">TODAY()</f>
-        <v>45511</v>
+        <v>46300</v>
       </c>
       <c r="F2" s="28" t="str">
         <f ca="1">TEXT(WEEKDAY(E2,1),"aaaa")</f>
-        <v>星期三</v>
+        <v>星期一</v>
       </c>
       <c r="G2" s="29"/>
       <c r="H2" s="30" t="s">
@@ -3342,7 +3342,9 @@
       <c r="O24" s="46"/>
     </row>
     <row r="25" spans="2:32" x14ac:dyDescent="0.15">
-      <c r="B25" s="51"/>
+      <c r="B25" s="45">
+        <v>45155</v>
+      </c>
       <c r="C25" s="52" t="s">
         <v>24</v>
       </c>
@@ -3412,7 +3414,9 @@
       <c r="O26" s="46"/>
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.15">
-      <c r="B27" s="51"/>
+      <c r="B27" s="45">
+        <v>45155</v>
+      </c>
       <c r="C27" s="52" t="s">
         <v>19</v>
       </c>
@@ -9019,11 +9023,11 @@
       </c>
       <c r="G2" s="27">
         <f ca="1">TODAY()</f>
-        <v>45511</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="77" t="str">
         <f ca="1">TEXT(WEEKDAY(每日用粉紀錄表!E2,1),"aaaa")</f>
-        <v>星期三</v>
+        <v>星期一</v>
       </c>
       <c r="I2" s="78"/>
       <c r="J2" s="23"/>
